--- a/Data/Rehires/Workday_Rehire_Belgium_Regression_PK14.xlsx
+++ b/Data/Rehires/Workday_Rehire_Belgium_Regression_PK14.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F715AF27-AA0B-4FDE-89DF-31105BD250E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C971991-EF37-4F88-B43A-83FEE0FA59EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,7 +11,6 @@
     <sheet name="Test_Data" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="82">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -272,9 +271,6 @@
   </si>
   <si>
     <t>Test5</t>
-  </si>
-  <si>
-    <t>Test failed for 'BelgiumSeven TwentyFiveMayTwentyEight' Employee:{10698332}Error: locator.press: Target page, context or browser has been closed</t>
   </si>
   <si>
     <t>BelgiumSeven</t>
@@ -1025,7 +1021,7 @@
       </c>
       <c r="J2" s="12">
         <f ca="1">TODAY()-3</f>
-        <v>45809</v>
+        <v>45814</v>
       </c>
       <c r="K2" s="13" t="s">
         <v>43</v>
@@ -1074,14 +1070,14 @@
       </c>
       <c r="Z2" s="22">
         <f ca="1">J2+60</f>
-        <v>45869</v>
+        <v>45874</v>
       </c>
       <c r="AA2" s="19" t="s">
         <v>44</v>
       </c>
       <c r="AB2" s="12">
         <f ca="1">J2-1</f>
-        <v>45808</v>
+        <v>45813</v>
       </c>
       <c r="AC2" s="13" t="s">
         <v>43</v>
@@ -1141,7 +1137,7 @@
       </c>
       <c r="J3" s="12">
         <f ca="1">TODAY()-3</f>
-        <v>45809</v>
+        <v>45814</v>
       </c>
       <c r="K3" s="13" t="s">
         <v>43</v>
@@ -1172,7 +1168,7 @@
       </c>
       <c r="T3" s="22">
         <f ca="1">J3+180</f>
-        <v>45989</v>
+        <v>45994</v>
       </c>
       <c r="U3" s="13" t="s">
         <v>49</v>
@@ -1191,15 +1187,15 @@
       </c>
       <c r="Z3" s="22">
         <f ca="1">J3+60</f>
-        <v>45869</v>
+        <v>45874</v>
       </c>
       <c r="AA3" s="12">
         <f ca="1">T3</f>
-        <v>45989</v>
+        <v>45994</v>
       </c>
       <c r="AB3" s="12">
         <f ca="1">J3-1</f>
-        <v>45808</v>
+        <v>45813</v>
       </c>
       <c r="AC3" s="13" t="s">
         <v>43</v>
@@ -1212,7 +1208,7 @@
       </c>
       <c r="AF3" s="24">
         <f ca="1">T3</f>
-        <v>45989</v>
+        <v>45994</v>
       </c>
       <c r="AG3" s="19" t="s">
         <v>56</v>
@@ -1264,7 +1260,7 @@
       </c>
       <c r="J4" s="12">
         <f ca="1">TODAY()-3</f>
-        <v>45809</v>
+        <v>45814</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>43</v>
@@ -1313,14 +1309,14 @@
       </c>
       <c r="Z4" s="22">
         <f ca="1">J4+60</f>
-        <v>45869</v>
+        <v>45874</v>
       </c>
       <c r="AA4" s="19" t="s">
         <v>44</v>
       </c>
       <c r="AB4" s="12">
         <f ca="1">J4-1</f>
-        <v>45808</v>
+        <v>45813</v>
       </c>
       <c r="AC4" s="13" t="s">
         <v>43</v>
@@ -1379,7 +1375,7 @@
       </c>
       <c r="J5" s="12">
         <f ca="1">TODAY()-3</f>
-        <v>45809</v>
+        <v>45814</v>
       </c>
       <c r="K5" s="13" t="s">
         <v>43</v>
@@ -1428,14 +1424,14 @@
       </c>
       <c r="Z5" s="22">
         <f ca="1">J5+60</f>
-        <v>45869</v>
+        <v>45874</v>
       </c>
       <c r="AA5" s="19" t="s">
         <v>44</v>
       </c>
       <c r="AB5" s="12">
         <f ca="1">J5-1</f>
-        <v>45808</v>
+        <v>45813</v>
       </c>
       <c r="AC5" s="13" t="s">
         <v>43</v>
@@ -1467,8 +1463,8 @@
       <c r="A6" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>79</v>
+      <c r="B6" s="1">
+        <v>10698332</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>69</v>
@@ -1480,7 +1476,7 @@
         <v>10698332</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>41</v>
@@ -1494,7 +1490,7 @@
       </c>
       <c r="J6" s="12">
         <f ca="1">TODAY()-3</f>
-        <v>45809</v>
+        <v>45814</v>
       </c>
       <c r="K6" s="13" t="s">
         <v>43</v>
@@ -1525,7 +1521,7 @@
       </c>
       <c r="T6" s="22">
         <f ca="1">J6+180</f>
-        <v>45989</v>
+        <v>45994</v>
       </c>
       <c r="U6" s="13" t="s">
         <v>49</v>
@@ -1534,7 +1530,7 @@
         <v>50</v>
       </c>
       <c r="W6" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="X6" s="13" t="s">
         <v>52</v>
@@ -1544,15 +1540,15 @@
       </c>
       <c r="Z6" s="22">
         <f ca="1">J6+60</f>
-        <v>45869</v>
+        <v>45874</v>
       </c>
       <c r="AA6" s="12">
         <f ca="1">T6</f>
-        <v>45989</v>
+        <v>45994</v>
       </c>
       <c r="AB6" s="12">
         <f ca="1">J6-1</f>
-        <v>45808</v>
+        <v>45813</v>
       </c>
       <c r="AC6" s="13" t="s">
         <v>43</v>
@@ -1565,7 +1561,7 @@
       </c>
       <c r="AF6" s="24">
         <f ca="1">T6</f>
-        <v>45989</v>
+        <v>45994</v>
       </c>
       <c r="AG6" s="19" t="s">
         <v>56</v>
@@ -1577,7 +1573,7 @@
       <c r="AJ6" s="12"/>
       <c r="AK6" s="12"/>
       <c r="AL6" s="28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:38" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/Data/Rehires/Workday_Rehire_Belgium_Regression_PK14.xlsx
+++ b/Data/Rehires/Workday_Rehire_Belgium_Regression_PK14.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C971991-EF37-4F88-B43A-83FEE0FA59EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33CBE757-C1B1-48F8-ABA5-B7D0643BE91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test_Data" sheetId="1" r:id="rId1"/>
@@ -808,78 +808,78 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BP18"/>
-  <sheetFormatPr defaultRowHeight="15.6" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.65" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.77734375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.44140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="48.6640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="36.77734375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.88671875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.453125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="7.54296875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.81640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.36328125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="24.453125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="48.6328125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="36.81640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.90625" style="1" customWidth="1"/>
     <col min="11" max="11" width="7" style="1" customWidth="1"/>
-    <col min="12" max="12" width="7.5546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="7.54296875" style="1" customWidth="1"/>
     <col min="13" max="13" width="13" style="1" customWidth="1"/>
-    <col min="14" max="14" width="18.6640625" style="2" customWidth="1"/>
-    <col min="15" max="15" width="8.88671875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="8.109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="20.5546875" style="1" customWidth="1"/>
-    <col min="18" max="18" width="31.109375" style="1" customWidth="1"/>
-    <col min="19" max="19" width="9.21875" style="1" customWidth="1"/>
-    <col min="20" max="20" width="18.5546875" style="1" customWidth="1"/>
-    <col min="21" max="21" width="26.44140625" style="1" customWidth="1"/>
-    <col min="22" max="22" width="16.77734375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="18.6328125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="8.90625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="8.08984375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="20.54296875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="31.08984375" style="1" customWidth="1"/>
+    <col min="19" max="19" width="9.1796875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="18.54296875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="26.453125" style="1" customWidth="1"/>
+    <col min="22" max="22" width="16.81640625" style="1" customWidth="1"/>
     <col min="23" max="23" width="17" style="1" customWidth="1"/>
-    <col min="24" max="24" width="29.33203125" style="1" customWidth="1"/>
-    <col min="25" max="25" width="20.88671875" style="1" customWidth="1"/>
+    <col min="24" max="24" width="29.36328125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="20.90625" style="1" customWidth="1"/>
     <col min="26" max="26" width="16" style="2" customWidth="1"/>
     <col min="27" max="27" width="16" style="1" customWidth="1"/>
-    <col min="28" max="28" width="18.5546875" style="1" customWidth="1"/>
+    <col min="28" max="28" width="18.54296875" style="1" customWidth="1"/>
     <col min="29" max="29" width="7" style="1" customWidth="1"/>
     <col min="30" max="30" width="6" style="1" customWidth="1"/>
-    <col min="31" max="31" width="12.77734375" style="1" customWidth="1"/>
-    <col min="32" max="32" width="15.109375" style="1" customWidth="1"/>
+    <col min="31" max="31" width="12.81640625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="15.08984375" style="1" customWidth="1"/>
     <col min="33" max="33" width="9" style="1" customWidth="1"/>
-    <col min="34" max="34" width="16.77734375" style="1" customWidth="1"/>
+    <col min="34" max="34" width="16.81640625" style="1" customWidth="1"/>
     <col min="35" max="35" width="21" style="1" customWidth="1"/>
     <col min="36" max="36" width="17" style="1" customWidth="1"/>
     <col min="37" max="37" width="21" style="1" customWidth="1"/>
-    <col min="38" max="38" width="17.5546875" customWidth="1"/>
-    <col min="39" max="40" width="22.44140625" style="1" customWidth="1"/>
-    <col min="41" max="41" width="18.21875" style="1" customWidth="1"/>
-    <col min="42" max="42" width="17.77734375" style="1" customWidth="1"/>
-    <col min="43" max="43" width="5.88671875" style="1" customWidth="1"/>
-    <col min="44" max="44" width="15.109375" style="1" customWidth="1"/>
+    <col min="38" max="38" width="17.54296875" customWidth="1"/>
+    <col min="39" max="40" width="22.453125" style="1" customWidth="1"/>
+    <col min="41" max="41" width="18.1796875" style="1" customWidth="1"/>
+    <col min="42" max="42" width="17.81640625" style="1" customWidth="1"/>
+    <col min="43" max="43" width="5.90625" style="1" customWidth="1"/>
+    <col min="44" max="44" width="15.08984375" style="1" customWidth="1"/>
     <col min="45" max="45" width="7" style="1" customWidth="1"/>
-    <col min="46" max="46" width="10.77734375" style="1" customWidth="1"/>
-    <col min="47" max="47" width="13.5546875" style="1" customWidth="1"/>
-    <col min="48" max="48" width="20.21875" style="1" customWidth="1"/>
-    <col min="49" max="49" width="9.88671875" style="1" customWidth="1"/>
-    <col min="50" max="50" width="11.88671875" style="1" customWidth="1"/>
-    <col min="51" max="51" width="15.88671875" style="1" customWidth="1"/>
+    <col min="46" max="46" width="10.81640625" style="1" customWidth="1"/>
+    <col min="47" max="47" width="13.54296875" style="1" customWidth="1"/>
+    <col min="48" max="48" width="20.1796875" style="1" customWidth="1"/>
+    <col min="49" max="49" width="9.90625" style="1" customWidth="1"/>
+    <col min="50" max="50" width="11.90625" style="1" customWidth="1"/>
+    <col min="51" max="51" width="15.90625" style="1" customWidth="1"/>
     <col min="52" max="52" width="15" style="1" customWidth="1"/>
-    <col min="53" max="53" width="16.33203125" style="2" customWidth="1"/>
-    <col min="54" max="54" width="53.6640625" style="2" customWidth="1"/>
-    <col min="55" max="55" width="23.77734375" style="2" customWidth="1"/>
+    <col min="53" max="53" width="16.36328125" style="2" customWidth="1"/>
+    <col min="54" max="54" width="53.6328125" style="2" customWidth="1"/>
+    <col min="55" max="55" width="23.81640625" style="2" customWidth="1"/>
     <col min="56" max="56" width="9" style="1" customWidth="1"/>
-    <col min="57" max="57" width="30.109375" style="1" customWidth="1"/>
-    <col min="58" max="58" width="20.33203125" style="1" customWidth="1"/>
-    <col min="59" max="59" width="14.44140625" style="1" customWidth="1"/>
-    <col min="60" max="60" width="17.109375" style="1" customWidth="1"/>
-    <col min="61" max="61" width="11.5546875" style="1" customWidth="1"/>
-    <col min="62" max="62" width="15.44140625" style="1" customWidth="1"/>
-    <col min="63" max="64" width="11.109375" style="1" customWidth="1"/>
-    <col min="65" max="65" width="16.6640625" style="1" customWidth="1"/>
-    <col min="66" max="66" width="18.109375" style="1" customWidth="1"/>
-    <col min="67" max="67" width="17.109375" style="1" customWidth="1"/>
-    <col min="68" max="68" width="16.5546875" style="1" customWidth="1"/>
-    <col min="69" max="69" width="16.109375" customWidth="1"/>
+    <col min="57" max="57" width="30.08984375" style="1" customWidth="1"/>
+    <col min="58" max="58" width="20.36328125" style="1" customWidth="1"/>
+    <col min="59" max="59" width="14.453125" style="1" customWidth="1"/>
+    <col min="60" max="60" width="17.08984375" style="1" customWidth="1"/>
+    <col min="61" max="61" width="11.54296875" style="1" customWidth="1"/>
+    <col min="62" max="62" width="15.453125" style="1" customWidth="1"/>
+    <col min="63" max="64" width="11.08984375" style="1" customWidth="1"/>
+    <col min="65" max="65" width="16.6328125" style="1" customWidth="1"/>
+    <col min="66" max="66" width="18.08984375" style="1" customWidth="1"/>
+    <col min="67" max="67" width="17.08984375" style="1" customWidth="1"/>
+    <col min="68" max="68" width="16.54296875" style="1" customWidth="1"/>
+    <col min="69" max="69" width="16.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="1" customFormat="1" ht="14.55" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" s="1" customFormat="1" ht="14.5" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -995,7 +995,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:38" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:38" s="1" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>38</v>
       </c>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="J2" s="12">
         <f ca="1">TODAY()-3</f>
-        <v>45814</v>
+        <v>45818</v>
       </c>
       <c r="K2" s="13" t="s">
         <v>43</v>
@@ -1070,14 +1070,14 @@
       </c>
       <c r="Z2" s="22">
         <f ca="1">J2+60</f>
-        <v>45874</v>
+        <v>45878</v>
       </c>
       <c r="AA2" s="19" t="s">
         <v>44</v>
       </c>
       <c r="AB2" s="12">
         <f ca="1">J2-1</f>
-        <v>45813</v>
+        <v>45817</v>
       </c>
       <c r="AC2" s="13" t="s">
         <v>43</v>
@@ -1111,7 +1111,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:38" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:38" s="1" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>58</v>
       </c>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="J3" s="12">
         <f ca="1">TODAY()-3</f>
-        <v>45814</v>
+        <v>45818</v>
       </c>
       <c r="K3" s="13" t="s">
         <v>43</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="T3" s="22">
         <f ca="1">J3+180</f>
-        <v>45994</v>
+        <v>45998</v>
       </c>
       <c r="U3" s="13" t="s">
         <v>49</v>
@@ -1187,15 +1187,15 @@
       </c>
       <c r="Z3" s="22">
         <f ca="1">J3+60</f>
-        <v>45874</v>
+        <v>45878</v>
       </c>
       <c r="AA3" s="12">
         <f ca="1">T3</f>
-        <v>45994</v>
+        <v>45998</v>
       </c>
       <c r="AB3" s="12">
         <f ca="1">J3-1</f>
-        <v>45813</v>
+        <v>45817</v>
       </c>
       <c r="AC3" s="13" t="s">
         <v>43</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AF3" s="24">
         <f ca="1">T3</f>
-        <v>45994</v>
+        <v>45998</v>
       </c>
       <c r="AG3" s="19" t="s">
         <v>56</v>
@@ -1229,7 +1229,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:38" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:38" s="1" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>67</v>
       </c>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="J4" s="12">
         <f ca="1">TODAY()-3</f>
-        <v>45814</v>
+        <v>45818</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>43</v>
@@ -1309,14 +1309,14 @@
       </c>
       <c r="Z4" s="22">
         <f ca="1">J4+60</f>
-        <v>45874</v>
+        <v>45878</v>
       </c>
       <c r="AA4" s="19" t="s">
         <v>44</v>
       </c>
       <c r="AB4" s="12">
         <f ca="1">J4-1</f>
-        <v>45813</v>
+        <v>45817</v>
       </c>
       <c r="AC4" s="13" t="s">
         <v>43</v>
@@ -1344,7 +1344,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:38" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:38" s="1" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>74</v>
       </c>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="J5" s="12">
         <f ca="1">TODAY()-3</f>
-        <v>45814</v>
+        <v>45818</v>
       </c>
       <c r="K5" s="13" t="s">
         <v>43</v>
@@ -1424,14 +1424,14 @@
       </c>
       <c r="Z5" s="22">
         <f ca="1">J5+60</f>
-        <v>45874</v>
+        <v>45878</v>
       </c>
       <c r="AA5" s="19" t="s">
         <v>44</v>
       </c>
       <c r="AB5" s="12">
         <f ca="1">J5-1</f>
-        <v>45813</v>
+        <v>45817</v>
       </c>
       <c r="AC5" s="13" t="s">
         <v>43</v>
@@ -1459,7 +1459,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:38" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:38" s="1" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>78</v>
       </c>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="J6" s="12">
         <f ca="1">TODAY()-3</f>
-        <v>45814</v>
+        <v>45818</v>
       </c>
       <c r="K6" s="13" t="s">
         <v>43</v>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="T6" s="22">
         <f ca="1">J6+180</f>
-        <v>45994</v>
+        <v>45998</v>
       </c>
       <c r="U6" s="13" t="s">
         <v>49</v>
@@ -1540,15 +1540,15 @@
       </c>
       <c r="Z6" s="22">
         <f ca="1">J6+60</f>
-        <v>45874</v>
+        <v>45878</v>
       </c>
       <c r="AA6" s="12">
         <f ca="1">T6</f>
-        <v>45994</v>
+        <v>45998</v>
       </c>
       <c r="AB6" s="12">
         <f ca="1">J6-1</f>
-        <v>45813</v>
+        <v>45817</v>
       </c>
       <c r="AC6" s="13" t="s">
         <v>43</v>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="AF6" s="24">
         <f ca="1">T6</f>
-        <v>45994</v>
+        <v>45998</v>
       </c>
       <c r="AG6" s="19" t="s">
         <v>56</v>
@@ -1576,18 +1576,18 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:38" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:38" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:38" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:38" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:38" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:38" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:38" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:38" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:38" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:38" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:38" s="1" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:38" s="1" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="9" spans="1:38" s="1" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="10" spans="1:38" s="1" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="1:38" s="1" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="12" spans="1:38" s="1" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="1:38" s="1" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="14" spans="1:38" s="1" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="15" spans="1:38" s="1" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:38" s="1" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="17" s="1" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="18" s="1" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AD6 P2:P6 K2:K6" xr:uid="{00000000-0002-0000-0000-000000000000}">

--- a/Data/Rehires/Workday_Rehire_Belgium_Regression_PK14.xlsx
+++ b/Data/Rehires/Workday_Rehire_Belgium_Regression_PK14.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C971991-EF37-4F88-B43A-83FEE0FA59EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58569797-E008-41C4-8744-5663ED6F44E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="90">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -147,13 +147,22 @@
     <t>Test1</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
     <t>Belgium</t>
   </si>
   <si>
+    <t>10698544</t>
+  </si>
+  <si>
     <t>BelgiumOne</t>
   </si>
   <si>
-    <t>TwentyFiveMayTwentyEight</t>
+    <t>TwentyFiveSixteen</t>
   </si>
   <si>
     <t>751 Retail Team 1 (Mupol Bypitu (10528834) (Inherited))</t>
@@ -162,9 +171,6 @@
     <t>ReHire</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Permanent</t>
   </si>
   <si>
@@ -192,10 +198,13 @@
     <t>BE Monthly</t>
   </si>
   <si>
+    <t>More than 3 Months</t>
+  </si>
+  <si>
     <t>Active</t>
   </si>
   <si>
-    <t>undefined</t>
+    <t>Contract Permanent</t>
   </si>
   <si>
     <t>Defaulted</t>
@@ -207,13 +216,16 @@
     <t>Test2</t>
   </si>
   <si>
+    <t>10698545</t>
+  </si>
+  <si>
     <t>BelgiumTwo</t>
   </si>
   <si>
     <t>751 Store Management (Mupol Bypitu (10528834))</t>
   </si>
   <si>
-    <t>Auto 72527049</t>
+    <t>Auto 46345385</t>
   </si>
   <si>
     <t>Fixed Term</t>
@@ -234,43 +246,43 @@
     <t>Test3</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'BelgiumFour TwentyFiveMayTwentyEight' Employee:{10698329}TimeoutError: page.waitForSelector: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for locator('button:has-text(\'Hire: BelgiumFour TwentyFiveMayTwentyEight\')') to be visible[22m
-</t>
+    <t>10698547</t>
+  </si>
+  <si>
+    <t>BelgiumFour</t>
+  </si>
+  <si>
+    <t>Auto 65305932</t>
+  </si>
+  <si>
+    <t>Part time</t>
+  </si>
+  <si>
+    <t>Variable | 20 | A20</t>
+  </si>
+  <si>
+    <t>Test4</t>
+  </si>
+  <si>
+    <t>10698546</t>
+  </si>
+  <si>
+    <t>BelgiumThree</t>
+  </si>
+  <si>
+    <t>Variable | 35 | A35</t>
+  </si>
+  <si>
+    <t>Test5</t>
+  </si>
+  <si>
+    <t>Test failed for 'BelgiumSeven TwentyFiveSixteen' Employee:{10698550}TypeError: Cannot read properties of undefined (reading 'match')</t>
   </si>
   <si>
     <t>Failed</t>
   </si>
   <si>
-    <t>BelgiumFour</t>
-  </si>
-  <si>
-    <t>Auto 82547733</t>
-  </si>
-  <si>
-    <t>Part time</t>
-  </si>
-  <si>
-    <t>Variable | 20 | A20</t>
-  </si>
-  <si>
-    <t>Test4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test failed for 'BelgiumThree TwentyFiveMayTwentyEight' Employee:{10698328}TimeoutError: locator.click: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for locator('//label[contains(.,\'Hire Date\')]/parent::div/following-sibling::div/descendant::input[@data-automation-id=\'dateSectionDay-input\']')[22m
-</t>
-  </si>
-  <si>
-    <t>BelgiumThree</t>
-  </si>
-  <si>
-    <t>Variable | 35 | A35</t>
-  </si>
-  <si>
-    <t>Test5</t>
+    <t>10698550</t>
   </si>
   <si>
     <t>BelgiumSeven</t>
@@ -280,6 +292,12 @@
   </si>
   <si>
     <t>Variable | 30 | A30</t>
+  </si>
+  <si>
+    <t>Test failed for 'BelgiumSeven TwentyFiveSixteen' Employee:{10698545}TypeError: Cannot read properties of undefined (reading 'match')</t>
+  </si>
+  <si>
+    <t>Test failed for 'BelgiumSeven TwentyFiveSixteen' Employee:{10698546}TypeError: Cannot read properties of undefined (reading 'match')</t>
   </si>
 </sst>
 </file>
@@ -325,7 +343,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -352,7 +370,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -365,6 +383,11 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -436,7 +459,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -460,7 +483,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -516,16 +539,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -838,7 +857,7 @@
     <col min="26" max="26" width="16" style="2" customWidth="1"/>
     <col min="27" max="27" width="16" style="1" customWidth="1"/>
     <col min="28" max="28" width="18.5546875" style="1" customWidth="1"/>
-    <col min="29" max="29" width="7" style="1" customWidth="1"/>
+    <col min="29" max="29" width="18.21875" style="1" customWidth="1"/>
     <col min="30" max="30" width="6" style="1" customWidth="1"/>
     <col min="31" max="31" width="12.77734375" style="1" customWidth="1"/>
     <col min="32" max="32" width="15.109375" style="1" customWidth="1"/>
@@ -999,44 +1018,49 @@
       <c r="A2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="6"/>
+      <c r="B2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>40</v>
+      </c>
       <c r="D2" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="I2" s="11" t="str">
+        <f t="shared" ref="I2:I6" si="0">F2 &amp; " " &amp; G2</f>
+        <v>BelgiumOne TwentyFiveSixteen</v>
+      </c>
+      <c r="J2" s="12">
+        <f t="shared" ref="J2:J6" ca="1" si="1">TODAY()-3</f>
+        <v>45828</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="L2" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="8">
-        <v>10698325</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="I2" s="11" t="str">
-        <f>F2 &amp; " " &amp; G2</f>
-        <v>BelgiumOne TwentyFiveMayTwentyEight</v>
-      </c>
-      <c r="J2" s="12">
-        <f ca="1">TODAY()-3</f>
-        <v>45814</v>
-      </c>
-      <c r="K2" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="L2" s="14" t="s">
-        <v>44</v>
-      </c>
       <c r="M2" s="15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N2" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O2" s="15" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P2" s="13">
         <v>751</v>
@@ -1045,55 +1069,55 @@
         <v>35</v>
       </c>
       <c r="R2" s="18" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S2" s="19">
         <v>5</v>
       </c>
       <c r="T2" s="13" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="U2" s="13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="V2" s="20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="W2" s="15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="X2" s="13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Y2" s="21" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z2" s="22">
-        <f ca="1">J2+60</f>
-        <v>45874</v>
+        <f t="shared" ref="Z2:Z6" ca="1" si="2">J2+60</f>
+        <v>45888</v>
       </c>
       <c r="AA2" s="19" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="AB2" s="12">
-        <f ca="1">J2-1</f>
-        <v>45813</v>
-      </c>
-      <c r="AC2" s="13" t="s">
-        <v>43</v>
+        <f t="shared" ref="AB2:AB6" ca="1" si="3">J2-1</f>
+        <v>45827</v>
+      </c>
+      <c r="AC2" s="18" t="s">
+        <v>56</v>
       </c>
       <c r="AD2" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="AE2" s="23" t="s">
-        <v>55</v>
+        <v>57</v>
+      </c>
+      <c r="AE2" s="20" t="s">
+        <v>58</v>
       </c>
       <c r="AF2" s="24" t="str">
-        <f>T2</f>
+        <f t="shared" ref="AF2:AF6" si="4">T2</f>
         <v>N/A</v>
       </c>
       <c r="AG2" s="19" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="AH2" s="19">
         <v>1</v>
@@ -1108,51 +1132,56 @@
         <v>44895</v>
       </c>
       <c r="AL2" s="25" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:38" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" s="6"/>
+        <v>61</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>83</v>
+      </c>
       <c r="D3" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" s="8">
-        <v>10698326</v>
+        <v>41</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>62</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I3" s="11" t="str">
-        <f>F3 &amp; " " &amp; G3</f>
-        <v>BelgiumTwo TwentyFiveMayTwentyEight</v>
+        <f t="shared" si="0"/>
+        <v>BelgiumTwo TwentyFiveSixteen</v>
       </c>
       <c r="J3" s="12">
-        <f ca="1">TODAY()-3</f>
-        <v>45814</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>45828</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="N3" s="16" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="O3" s="15" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P3" s="13">
         <v>751</v>
@@ -1161,57 +1190,57 @@
         <v>35</v>
       </c>
       <c r="R3" s="18" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="S3" s="19">
         <v>5</v>
       </c>
       <c r="T3" s="22">
         <f ca="1">J3+180</f>
-        <v>45994</v>
+        <v>46008</v>
       </c>
       <c r="U3" s="13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="V3" s="20" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="W3" s="15" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="X3" s="13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Y3" s="21" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z3" s="22">
-        <f ca="1">J3+60</f>
-        <v>45874</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45888</v>
       </c>
       <c r="AA3" s="12">
         <f ca="1">T3</f>
-        <v>45994</v>
+        <v>46008</v>
       </c>
       <c r="AB3" s="12">
-        <f ca="1">J3-1</f>
-        <v>45813</v>
-      </c>
-      <c r="AC3" s="13" t="s">
-        <v>43</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>45827</v>
+      </c>
+      <c r="AC3" s="18" t="s">
+        <v>56</v>
       </c>
       <c r="AD3" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="AE3" s="23" t="s">
-        <v>55</v>
+        <v>57</v>
+      </c>
+      <c r="AE3" s="20" t="s">
+        <v>66</v>
       </c>
       <c r="AF3" s="24">
-        <f ca="1">T3</f>
-        <v>45994</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>46008</v>
       </c>
       <c r="AG3" s="19" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="AH3" s="19">
         <v>1</v>
@@ -1226,56 +1255,56 @@
         <v>44895</v>
       </c>
       <c r="AL3" s="25" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:38" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="I4" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>BelgiumFour TwentyFiveSixteen</v>
+      </c>
+      <c r="J4" s="12">
+        <f t="shared" ca="1" si="1"/>
+        <v>45828</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="L4" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="M4" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="N4" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" s="27">
-        <v>10698329</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="I4" s="11" t="str">
-        <f>F4 &amp; " " &amp; G4</f>
-        <v>BelgiumFour TwentyFiveMayTwentyEight</v>
-      </c>
-      <c r="J4" s="12">
-        <f ca="1">TODAY()-3</f>
-        <v>45814</v>
-      </c>
-      <c r="K4" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="L4" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="M4" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="N4" s="16" t="s">
-        <v>63</v>
-      </c>
       <c r="O4" s="15" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="P4" s="13">
         <v>751</v>
@@ -1284,55 +1313,55 @@
         <v>20</v>
       </c>
       <c r="R4" s="18" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S4" s="19">
         <v>5</v>
       </c>
       <c r="T4" s="13" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="U4" s="13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="V4" s="20" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="W4" s="15">
         <v>251</v>
       </c>
       <c r="X4" s="13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Y4" s="21" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z4" s="22">
-        <f ca="1">J4+60</f>
-        <v>45874</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45888</v>
       </c>
       <c r="AA4" s="19" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="AB4" s="12">
-        <f ca="1">J4-1</f>
-        <v>45813</v>
-      </c>
-      <c r="AC4" s="13" t="s">
-        <v>43</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>45827</v>
+      </c>
+      <c r="AC4" s="18" t="s">
+        <v>56</v>
       </c>
       <c r="AD4" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="AE4" s="23" t="s">
-        <v>55</v>
+        <v>57</v>
+      </c>
+      <c r="AE4" s="20" t="s">
+        <v>58</v>
       </c>
       <c r="AF4" s="24" t="str">
-        <f>T4</f>
+        <f t="shared" si="4"/>
         <v>N/A</v>
       </c>
       <c r="AG4" s="19" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="AH4" s="19">
         <v>1</v>
@@ -1340,57 +1369,57 @@
       <c r="AI4" s="12"/>
       <c r="AJ4" s="12"/>
       <c r="AK4" s="12"/>
-      <c r="AL4" s="28" t="s">
-        <v>73</v>
+      <c r="AL4" s="26" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:38" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>69</v>
+        <v>77</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>83</v>
       </c>
       <c r="D5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="I5" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>BelgiumThree TwentyFiveSixteen</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" ca="1" si="1"/>
+        <v>45828</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="L5" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="27">
-        <v>10698328</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5" s="11" t="str">
-        <f>F5 &amp; " " &amp; G5</f>
-        <v>BelgiumThree TwentyFiveMayTwentyEight</v>
-      </c>
-      <c r="J5" s="12">
-        <f ca="1">TODAY()-3</f>
-        <v>45814</v>
-      </c>
-      <c r="K5" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="L5" s="14" t="s">
-        <v>44</v>
-      </c>
       <c r="M5" s="15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N5" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O5" s="15" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P5" s="13">
         <v>751</v>
@@ -1399,55 +1428,55 @@
         <v>35</v>
       </c>
       <c r="R5" s="18" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="S5" s="19">
         <v>5</v>
       </c>
       <c r="T5" s="13" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="U5" s="13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="V5" s="20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="W5" s="15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="X5" s="13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Y5" s="21" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z5" s="22">
-        <f ca="1">J5+60</f>
-        <v>45874</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45888</v>
       </c>
       <c r="AA5" s="19" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="AB5" s="12">
-        <f ca="1">J5-1</f>
-        <v>45813</v>
-      </c>
-      <c r="AC5" s="13" t="s">
-        <v>43</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>45827</v>
+      </c>
+      <c r="AC5" s="18" t="s">
+        <v>56</v>
       </c>
       <c r="AD5" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="AE5" s="23" t="s">
-        <v>55</v>
+        <v>57</v>
+      </c>
+      <c r="AE5" s="20" t="s">
+        <v>58</v>
       </c>
       <c r="AF5" s="24" t="str">
-        <f>T5</f>
+        <f t="shared" si="4"/>
         <v>N/A</v>
       </c>
       <c r="AG5" s="19" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="AH5" s="19">
         <v>1</v>
@@ -1455,57 +1484,57 @@
       <c r="AI5" s="12"/>
       <c r="AJ5" s="12"/>
       <c r="AK5" s="12"/>
-      <c r="AL5" s="28" t="s">
-        <v>77</v>
+      <c r="AL5" s="26" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:38" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B6" s="1">
-        <v>10698332</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>69</v>
+        <v>81</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>83</v>
       </c>
       <c r="D6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>BelgiumSeven TwentyFiveSixteen</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" ca="1" si="1"/>
+        <v>45828</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="27">
-        <v>10698332</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" s="11" t="str">
-        <f>F6 &amp; " " &amp; G6</f>
-        <v>BelgiumSeven TwentyFiveMayTwentyEight</v>
-      </c>
-      <c r="J6" s="12">
-        <f ca="1">TODAY()-3</f>
-        <v>45814</v>
-      </c>
-      <c r="K6" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="L6" s="14" t="s">
-        <v>44</v>
-      </c>
       <c r="M6" s="15" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="N6" s="16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O6" s="15" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="P6" s="13">
         <v>751</v>
@@ -1514,57 +1543,57 @@
         <v>30</v>
       </c>
       <c r="R6" s="18" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S6" s="19">
         <v>5</v>
       </c>
       <c r="T6" s="22">
         <f ca="1">J6+180</f>
-        <v>45994</v>
+        <v>46008</v>
       </c>
       <c r="U6" s="13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="V6" s="20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="W6" s="15" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="X6" s="13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Y6" s="21" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z6" s="22">
-        <f ca="1">J6+60</f>
-        <v>45874</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>45888</v>
       </c>
       <c r="AA6" s="12">
         <f ca="1">T6</f>
-        <v>45994</v>
+        <v>46008</v>
       </c>
       <c r="AB6" s="12">
-        <f ca="1">J6-1</f>
-        <v>45813</v>
-      </c>
-      <c r="AC6" s="13" t="s">
-        <v>43</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>45827</v>
+      </c>
+      <c r="AC6" s="18" t="s">
+        <v>56</v>
       </c>
       <c r="AD6" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="AE6" s="23" t="s">
-        <v>55</v>
+        <v>57</v>
+      </c>
+      <c r="AE6" s="20" t="s">
+        <v>66</v>
       </c>
       <c r="AF6" s="24">
-        <f ca="1">T6</f>
-        <v>45994</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>46008</v>
       </c>
       <c r="AG6" s="19" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="AH6" s="19">
         <v>1</v>
@@ -1572,8 +1601,8 @@
       <c r="AI6" s="12"/>
       <c r="AJ6" s="12"/>
       <c r="AK6" s="12"/>
-      <c r="AL6" s="28" t="s">
-        <v>81</v>
+      <c r="AL6" s="26" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:38" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1590,7 +1619,7 @@
     <row r="18" s="1" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AD6 P2:P6 K2:K6" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2:AD6 P2:P6 K2:K6" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT($D2)</formula1>
     </dataValidation>
   </dataValidations>
